--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.698006789641704</v>
+        <v>5.590857759015498</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.336946666666667</v>
+        <v>5.217632495737237</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.540480409916791</v>
+        <v>6.461716706664774</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.664914850450051</v>
+        <v>1.658797002892988</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>123511.2032224126</v>
+        <v>126273.0517276428</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.589032003223516</v>
+        <v>2.674078864470835</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>634.1</v>
+        <v>577.2735499194329</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1588.766666666666</v>
+        <v>1585.936031282518</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2668.473333333333</v>
+        <v>2608.816247868619</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.336946666666667</v>
+        <v>5.217632495737237</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.336946666666667</v>
+        <v>5.217632495737237</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.321885</v>
+        <v>4.222275025356745</v>
       </c>
       <c r="F11" t="n">
-        <v>3.417405423989779</v>
+        <v>3.338641720737761</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.540480409916791</v>
+        <v>6.461716706664774</v>
       </c>
     </row>
     <row r="13">
@@ -1064,11 +1064,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.096819787627783</v>
+        <v>4.011100563126818</v>
       </c>
       <c r="C2" t="n">
-        <v>4.708430951624188</v>
+        <v>4.611996824060603</v>
       </c>
       <c r="D2" t="n">
-        <v>5.320042115620593</v>
+        <v>5.212893084994387</v>
       </c>
       <c r="E2" t="n">
-        <v>5.931653279616997</v>
+        <v>5.81378934592817</v>
       </c>
       <c r="F2" t="n">
-        <v>6.543264443613402</v>
+        <v>6.414685606861952</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.285802124638339</v>
+        <v>4.200082900137374</v>
       </c>
       <c r="C3" t="n">
-        <v>4.897413288634744</v>
+        <v>4.800979161071158</v>
       </c>
       <c r="D3" t="n">
-        <v>5.509024452631149</v>
+        <v>5.401875422004943</v>
       </c>
       <c r="E3" t="n">
-        <v>6.120635616627553</v>
+        <v>6.002771682938726</v>
       </c>
       <c r="F3" t="n">
-        <v>6.732246780623957</v>
+        <v>6.603667943872507</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.474784461648895</v>
+        <v>4.389065237147928</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086395625645299</v>
+        <v>4.989961498081714</v>
       </c>
       <c r="D4" t="n">
-        <v>5.698006789641704</v>
+        <v>5.590857759015498</v>
       </c>
       <c r="E4" t="n">
-        <v>6.309617953638108</v>
+        <v>6.191754019949281</v>
       </c>
       <c r="F4" t="n">
-        <v>6.921229117634512</v>
+        <v>6.792650280883063</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.66376679865945</v>
+        <v>4.578047574158484</v>
       </c>
       <c r="C5" t="n">
-        <v>5.275377962655854</v>
+        <v>5.178943835092269</v>
       </c>
       <c r="D5" t="n">
-        <v>5.886989126652259</v>
+        <v>5.779840096026053</v>
       </c>
       <c r="E5" t="n">
-        <v>6.498600290648664</v>
+        <v>6.380736356959837</v>
       </c>
       <c r="F5" t="n">
-        <v>7.110211454645068</v>
+        <v>6.981632617893618</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.852749135670006</v>
+        <v>4.76702991116904</v>
       </c>
       <c r="C6" t="n">
-        <v>5.46436029966641</v>
+        <v>5.367926172102825</v>
       </c>
       <c r="D6" t="n">
-        <v>6.075971463662816</v>
+        <v>5.968822433036609</v>
       </c>
       <c r="E6" t="n">
-        <v>6.68758262765922</v>
+        <v>6.569718693970392</v>
       </c>
       <c r="F6" t="n">
-        <v>7.299193791655624</v>
+        <v>7.170614954904174</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.7</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>5.87</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5.93</v>
+        <v>5.83</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126273.0517276428</v>
+        <v>113529.6484832117</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.674078864470835</v>
+        <v>2.404212374264656</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.36</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>113529.6484832117</v>
+        <v>116528.0963054308</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.404212374264656</v>
+        <v>2.467710371960226</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>116528.0963054308</v>
+        <v>110531.2006609926</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.467710371960226</v>
+        <v>2.340714376569084</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.28</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>110531.2006609926</v>
+        <v>108657.1707721057</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.340714376569084</v>
+        <v>2.301028128009351</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.590857759015498</v>
+        <v>5.662873577197971</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.461716706664774</v>
+        <v>6.701769433939684</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108657.1707721057</v>
+        <v>95335.86163496309</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.301028128009351</v>
+        <v>2.018923350122551</v>
       </c>
     </row>
   </sheetData>
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.222275025356745</v>
+        <v>4.525862148481071</v>
       </c>
       <c r="F11" t="n">
-        <v>3.338641720737761</v>
+        <v>3.578694448012672</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.461716706664774</v>
+        <v>6.701769433939684</v>
       </c>
     </row>
     <row r="13">
@@ -1065,7 +1065,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.011100563126818</v>
+        <v>4.026565683786297</v>
       </c>
       <c r="C2" t="n">
-        <v>4.611996824060603</v>
+        <v>4.614016346096864</v>
       </c>
       <c r="D2" t="n">
-        <v>5.212893084994387</v>
+        <v>5.20146700840743</v>
       </c>
       <c r="E2" t="n">
-        <v>5.81378934592817</v>
+        <v>5.788917670717995</v>
       </c>
       <c r="F2" t="n">
-        <v>6.414685606861952</v>
+        <v>6.37636833302856</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.200082900137374</v>
+        <v>4.257268968181567</v>
       </c>
       <c r="C3" t="n">
-        <v>4.800979161071158</v>
+        <v>4.844719630492134</v>
       </c>
       <c r="D3" t="n">
-        <v>5.401875422004943</v>
+        <v>5.4321702928027</v>
       </c>
       <c r="E3" t="n">
-        <v>6.002771682938726</v>
+        <v>6.019620955113266</v>
       </c>
       <c r="F3" t="n">
-        <v>6.603667943872507</v>
+        <v>6.607071617423831</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.389065237147928</v>
+        <v>4.487972252576838</v>
       </c>
       <c r="C4" t="n">
-        <v>4.989961498081714</v>
+        <v>5.075422914887405</v>
       </c>
       <c r="D4" t="n">
-        <v>5.590857759015498</v>
+        <v>5.662873577197971</v>
       </c>
       <c r="E4" t="n">
-        <v>6.191754019949281</v>
+        <v>6.250324239508537</v>
       </c>
       <c r="F4" t="n">
-        <v>6.792650280883063</v>
+        <v>6.837774901819101</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.578047574158484</v>
+        <v>4.718675536972108</v>
       </c>
       <c r="C5" t="n">
-        <v>5.178943835092269</v>
+        <v>5.306126199282675</v>
       </c>
       <c r="D5" t="n">
-        <v>5.779840096026053</v>
+        <v>5.893576861593241</v>
       </c>
       <c r="E5" t="n">
-        <v>6.380736356959837</v>
+        <v>6.481027523903807</v>
       </c>
       <c r="F5" t="n">
-        <v>6.981632617893618</v>
+        <v>7.068478186214371</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.76702991116904</v>
+        <v>4.949378821367379</v>
       </c>
       <c r="C6" t="n">
-        <v>5.367926172102825</v>
+        <v>5.536829483677945</v>
       </c>
       <c r="D6" t="n">
-        <v>5.968822433036609</v>
+        <v>6.124280145988513</v>
       </c>
       <c r="E6" t="n">
-        <v>6.569718693970392</v>
+        <v>6.711730808299077</v>
       </c>
       <c r="F6" t="n">
-        <v>7.170614954904174</v>
+        <v>7.299181470609642</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.59</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>5.77</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95335.86163496309</v>
+        <v>95335.86163496308</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.23</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95335.86163496308</v>
+        <v>87353.20783538384</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.018923350122551</v>
+        <v>1.849875041589672</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.97</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87353.20783538384</v>
+        <v>83975.93122786956</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.849875041589672</v>
+        <v>1.778354603364224</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83975.93122786956</v>
+        <v>83975.93122786954</v>
       </c>
     </row>
     <row r="16">
@@ -1278,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1294,13 +1294,6 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
           <t>LR2 FFA forward curve is CONSTRUCTED (no market anchor) — built from the 12M TC + spot, not a Baltic / $MT / Worldscale series. Treat its dividend-strip contribution as indicative.</t>
         </is>
       </c>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83975.93122786954</v>
+        <v>83975.93122786956</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83975.93122786956</v>
+        <v>83975.93122786954</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.86</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83975.93122786954</v>
+        <v>77221.37801284091</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.778354603364224</v>
+        <v>1.635313726913326</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77221.37801284091</v>
+        <v>77221.37801284093</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.662873577197971</v>
+        <v>5.986620768560386</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.217632495737237</v>
+        <v>5.57175176175691</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.701769433939684</v>
+        <v>6.954648451101832</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>77221.37801284093</v>
+        <v>67495.0443103367</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.635313726913326</v>
+        <v>1.429339585742212</v>
       </c>
     </row>
   </sheetData>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146.5</v>
+        <v>146.457</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>475</v>
+        <v>362.884</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-943.5</v>
+        <v>-953.932</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-35.9</v>
+        <v>-71.59699999999999</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-405</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2608.816247868619</v>
+        <v>2815.528247868619</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>500000000</v>
+        <v>505321911</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.217632495737237</v>
+        <v>5.57175176175691</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.217632495737237</v>
+        <v>5.57175176175691</v>
       </c>
     </row>
     <row r="16">
@@ -843,13 +843,13 @@
         <v>22000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5562755877875</v>
+        <v>0.5504170467164841</v>
       </c>
       <c r="E2" t="n">
-        <v>0.44502047023</v>
+        <v>0.4403336373731873</v>
       </c>
       <c r="F2" t="n">
-        <v>0.433560035918927</v>
+        <v>0.4289939011955163</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>30000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7383243200375</v>
+        <v>0.73054849192706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.59065945603</v>
+        <v>0.584438793541648</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5606291454576962</v>
+        <v>0.5547247539179991</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>28000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6756838960375</v>
+        <v>0.6685677795965392</v>
       </c>
       <c r="E4" t="n">
-        <v>0.54054711683</v>
+        <v>0.5348542236772315</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4998518699658532</v>
+        <v>0.4945875679293999</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>19000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4498580492875</v>
+        <v>0.4451202683822472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.35988643943</v>
+        <v>0.3560962147057978</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3242220175045045</v>
+        <v>0.3208074006358538</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>18000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4060809347875</v>
+        <v>0.401804202378531</v>
       </c>
       <c r="E6" t="n">
-        <v>0.32486474783</v>
+        <v>0.3214433619028248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2851339061404962</v>
+        <v>0.2821309544803176</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>23000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5377681897875001</v>
+        <v>0.5321045635279211</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4302145518300001</v>
+        <v>0.4256836508223369</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3678752988815517</v>
+        <v>0.3640009376929152</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6005865695375</v>
+        <v>0.5942613574275627</v>
       </c>
       <c r="E8" t="n">
-        <v>0.48046925563</v>
+        <v>0.4754090859420502</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4002675567702632</v>
+        <v>0.396052049255255</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>18000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3873955810375</v>
+        <v>0.3833156376208472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3099164648300001</v>
+        <v>0.3066525100966778</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2515351552877202</v>
+        <v>0.2488860564050627</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.123074985927012</v>
+        <v>3.09018362151232</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.525862148481071</v>
+        <v>4.887266949009332</v>
       </c>
       <c r="F11" t="n">
-        <v>3.578694448012672</v>
+        <v>3.864464829589512</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.701769433939684</v>
+        <v>6.954648451101832</v>
       </c>
     </row>
     <row r="13">
@@ -1065,7 +1065,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.026565683786297</v>
+        <v>4.367546018592069</v>
       </c>
       <c r="C2" t="n">
-        <v>4.614016346096864</v>
+        <v>4.948809812544759</v>
       </c>
       <c r="D2" t="n">
-        <v>5.20146700840743</v>
+        <v>5.530073606497449</v>
       </c>
       <c r="E2" t="n">
-        <v>5.788917670717995</v>
+        <v>6.111337400450138</v>
       </c>
       <c r="F2" t="n">
-        <v>6.37636833302856</v>
+        <v>6.692601194402825</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.257268968181567</v>
+        <v>4.595819599623538</v>
       </c>
       <c r="C3" t="n">
-        <v>4.844719630492134</v>
+        <v>5.177083393576228</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4321702928027</v>
+        <v>5.758347187528917</v>
       </c>
       <c r="E3" t="n">
-        <v>6.019620955113266</v>
+        <v>6.339610981481606</v>
       </c>
       <c r="F3" t="n">
-        <v>6.607071617423831</v>
+        <v>6.920874775434294</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.487972252576838</v>
+        <v>4.824093180655007</v>
       </c>
       <c r="C4" t="n">
-        <v>5.075422914887405</v>
+        <v>5.405356974607697</v>
       </c>
       <c r="D4" t="n">
-        <v>5.662873577197971</v>
+        <v>5.986620768560386</v>
       </c>
       <c r="E4" t="n">
-        <v>6.250324239508537</v>
+        <v>6.567884562513076</v>
       </c>
       <c r="F4" t="n">
-        <v>6.837774901819101</v>
+        <v>7.149148356465762</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.718675536972108</v>
+        <v>5.052366761686475</v>
       </c>
       <c r="C5" t="n">
-        <v>5.306126199282675</v>
+        <v>5.633630555639166</v>
       </c>
       <c r="D5" t="n">
-        <v>5.893576861593241</v>
+        <v>6.214894349591855</v>
       </c>
       <c r="E5" t="n">
-        <v>6.481027523903807</v>
+        <v>6.796158143544544</v>
       </c>
       <c r="F5" t="n">
-        <v>7.068478186214371</v>
+        <v>7.377421937497231</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.949378821367379</v>
+        <v>5.280640342717945</v>
       </c>
       <c r="C6" t="n">
-        <v>5.536829483677945</v>
+        <v>5.861904136670635</v>
       </c>
       <c r="D6" t="n">
-        <v>6.124280145988513</v>
+        <v>6.443167930623324</v>
       </c>
       <c r="E6" t="n">
-        <v>6.711730808299077</v>
+        <v>7.024431724576013</v>
       </c>
       <c r="F6" t="n">
-        <v>7.299181470609642</v>
+        <v>7.605695518528701</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.66</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>5.68</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5.69</v>
+        <v>6.01</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.64</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67495.0443103367</v>
+        <v>65012.69977319527</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.429339585742212</v>
+        <v>1.376771084622733</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.56</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65012.69977319527</v>
+        <v>79286.18086175837</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.376771084622733</v>
+        <v>1.679039966059731</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.02</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79286.18086175837</v>
+        <v>87043.50754032528</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.679039966059731</v>
+        <v>1.8433165320581</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.27</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87043.50754032528</v>
+        <v>88594.97287603869</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8433165320581</v>
+        <v>1.876171845257774</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88594.97287603869</v>
+        <v>88594.97287603868</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.32</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88594.97287603868</v>
+        <v>93559.66195032149</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.876171845257774</v>
+        <v>1.98130884749673</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.48</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93559.66195032149</v>
+        <v>86422.92140603994</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.98130884749673</v>
+        <v>1.830174406778231</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.986620768560386</v>
+        <v>5.985991940669319</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.57175176175691</v>
+        <v>5.570805778888315</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.954648451101832</v>
+        <v>6.954759651491665</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.658797002892988</v>
+        <v>1.658240668100722</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86422.92140603994</v>
+        <v>86361.79470331399</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.830174406778231</v>
+        <v>1.830587613524424</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>577.2735499194329</v>
+        <v>574.273828032541</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1585.936031282518</v>
+        <v>1588.457727298479</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2815.528247868619</v>
+        <v>2815.050221997687</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.57175176175691</v>
+        <v>5.570805778888315</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.57175176175691</v>
+        <v>5.570805778888315</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.887266949009332</v>
+        <v>4.88740758063982</v>
       </c>
       <c r="F11" t="n">
-        <v>3.864464829589512</v>
+        <v>3.864576029979346</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.954648451101832</v>
+        <v>6.954759651491665</v>
       </c>
     </row>
     <row r="13">
@@ -1064,11 +1064,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.367546018592069</v>
+        <v>4.367042956279215</v>
       </c>
       <c r="C2" t="n">
-        <v>4.948809812544759</v>
+        <v>4.948243867442798</v>
       </c>
       <c r="D2" t="n">
-        <v>5.530073606497449</v>
+        <v>5.529444778606382</v>
       </c>
       <c r="E2" t="n">
-        <v>6.111337400450138</v>
+        <v>6.110645689769965</v>
       </c>
       <c r="F2" t="n">
-        <v>6.692601194402825</v>
+        <v>6.691846600933546</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.595819599623538</v>
+        <v>4.595316537310684</v>
       </c>
       <c r="C3" t="n">
-        <v>5.177083393576228</v>
+        <v>5.176517448474267</v>
       </c>
       <c r="D3" t="n">
-        <v>5.758347187528917</v>
+        <v>5.757718359637851</v>
       </c>
       <c r="E3" t="n">
-        <v>6.339610981481606</v>
+        <v>6.338919270801433</v>
       </c>
       <c r="F3" t="n">
-        <v>6.920874775434294</v>
+        <v>6.920120181965014</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.824093180655007</v>
+        <v>4.823590118342153</v>
       </c>
       <c r="C4" t="n">
-        <v>5.405356974607697</v>
+        <v>5.404791029505736</v>
       </c>
       <c r="D4" t="n">
-        <v>5.986620768560386</v>
+        <v>5.985991940669319</v>
       </c>
       <c r="E4" t="n">
-        <v>6.567884562513076</v>
+        <v>6.567192851832903</v>
       </c>
       <c r="F4" t="n">
-        <v>7.149148356465762</v>
+        <v>7.148393762996483</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.052366761686475</v>
+        <v>5.051863699373622</v>
       </c>
       <c r="C5" t="n">
-        <v>5.633630555639166</v>
+        <v>5.633064610537205</v>
       </c>
       <c r="D5" t="n">
-        <v>6.214894349591855</v>
+        <v>6.214265521700788</v>
       </c>
       <c r="E5" t="n">
-        <v>6.796158143544544</v>
+        <v>6.795466432864371</v>
       </c>
       <c r="F5" t="n">
-        <v>7.377421937497231</v>
+        <v>7.376667344027952</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.280640342717945</v>
+        <v>5.280137280405091</v>
       </c>
       <c r="C6" t="n">
-        <v>5.861904136670635</v>
+        <v>5.861338191568674</v>
       </c>
       <c r="D6" t="n">
-        <v>6.443167930623324</v>
+        <v>6.442539102732256</v>
       </c>
       <c r="E6" t="n">
-        <v>7.024431724576013</v>
+        <v>7.023740013895841</v>
       </c>
       <c r="F6" t="n">
-        <v>7.605695518528701</v>
+        <v>7.604940925059421</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86361.79470331399</v>
+        <v>86361.79470331401</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86361.79470331401</v>
+        <v>86361.79470331399</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.25</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86361.79470331401</v>
+        <v>88841.82355743732</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.830587613524424</v>
+        <v>1.883156114643902</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88841.82355743732</v>
+        <v>88841.82355743731</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.33</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88841.82355743731</v>
+        <v>98761.93897393053</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.883156114643902</v>
+        <v>2.093430119121814</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98761.93897393053</v>
+        <v>98761.93897393052</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98761.93897393052</v>
+        <v>98761.93897393053</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98761.93897393052</v>
+        <v>99381.94618746135</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.093430119121814</v>
+        <v>2.106572244401684</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.67</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>99381.94618746135</v>
+        <v>94421.8884792147</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.106572244401684</v>
+        <v>2.001435242162727</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94421.8884792147</v>
+        <v>94421.88847921471</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94421.88847921471</v>
+        <v>94421.8884792147</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.985991940669319</v>
+        <v>5.980515110150819</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.570805778888315</v>
+        <v>5.564559894628247</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.954759651491665</v>
+        <v>6.951077279703486</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.658240668100722</v>
+        <v>1.657880482611522</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94421.8884792147</v>
+        <v>94534.4894198001</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.001435242162727</v>
+        <v>2.005034101803266</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>574.273828032541</v>
+        <v>571.1176458623593</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2815.050221997687</v>
+        <v>2811.894039827504</v>
       </c>
     </row>
     <row r="13">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.570805778888315</v>
+        <v>5.564559894628247</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.570805778888315</v>
+        <v>5.564559894628247</v>
       </c>
     </row>
     <row r="16">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.88740758063982</v>
+        <v>4.882750601024807</v>
       </c>
       <c r="F11" t="n">
-        <v>3.864576029979346</v>
+        <v>3.860893658191166</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.954759651491665</v>
+        <v>6.951077279703486</v>
       </c>
     </row>
     <row r="13">
@@ -1064,8 +1064,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.367042956279215</v>
+        <v>4.362661491864415</v>
       </c>
       <c r="C2" t="n">
-        <v>4.948243867442798</v>
+        <v>4.943314719976149</v>
       </c>
       <c r="D2" t="n">
-        <v>5.529444778606382</v>
+        <v>5.52396794808788</v>
       </c>
       <c r="E2" t="n">
-        <v>6.110645689769965</v>
+        <v>6.104621176199614</v>
       </c>
       <c r="F2" t="n">
-        <v>6.691846600933546</v>
+        <v>6.685274404311345</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.595316537310684</v>
+        <v>4.590935072895884</v>
       </c>
       <c r="C3" t="n">
-        <v>5.176517448474267</v>
+        <v>5.171588301007617</v>
       </c>
       <c r="D3" t="n">
-        <v>5.757718359637851</v>
+        <v>5.752241529119349</v>
       </c>
       <c r="E3" t="n">
-        <v>6.338919270801433</v>
+        <v>6.332894757231083</v>
       </c>
       <c r="F3" t="n">
-        <v>6.920120181965014</v>
+        <v>6.913547985342813</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.823590118342153</v>
+        <v>4.819208653927353</v>
       </c>
       <c r="C4" t="n">
-        <v>5.404791029505736</v>
+        <v>5.399861882039087</v>
       </c>
       <c r="D4" t="n">
-        <v>5.985991940669319</v>
+        <v>5.980515110150819</v>
       </c>
       <c r="E4" t="n">
-        <v>6.567192851832903</v>
+        <v>6.561168338262552</v>
       </c>
       <c r="F4" t="n">
-        <v>7.148393762996483</v>
+        <v>7.141821566374283</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.051863699373622</v>
+        <v>5.047482234958822</v>
       </c>
       <c r="C5" t="n">
-        <v>5.633064610537205</v>
+        <v>5.628135463070555</v>
       </c>
       <c r="D5" t="n">
-        <v>6.214265521700788</v>
+        <v>6.208788691182287</v>
       </c>
       <c r="E5" t="n">
-        <v>6.795466432864371</v>
+        <v>6.789441919294021</v>
       </c>
       <c r="F5" t="n">
-        <v>7.376667344027952</v>
+        <v>7.370095147405751</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.280137280405091</v>
+        <v>5.275755815990291</v>
       </c>
       <c r="C6" t="n">
-        <v>5.861338191568674</v>
+        <v>5.856409044102024</v>
       </c>
       <c r="D6" t="n">
-        <v>6.442539102732256</v>
+        <v>6.437062272213756</v>
       </c>
       <c r="E6" t="n">
-        <v>7.023740013895841</v>
+        <v>7.017715500325489</v>
       </c>
       <c r="F6" t="n">
-        <v>7.604940925059421</v>
+        <v>7.598368728437221</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.99</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.980515110150819</v>
+        <v>5.714874441889228</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.951077279703486</v>
+        <v>6.065608385498185</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22000</v>
+        <v>29250</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.657880482611522</v>
+        <v>1.792448433177855</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94534.4894198001</v>
+        <v>96485.20361670371</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.005034101803266</v>
+        <v>2.42903164965372</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +793,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="C2" t="n">
-        <v>22000</v>
+        <v>29300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5504170467164841</v>
+        <v>0.5156937612858628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4403336373731873</v>
+        <v>0.4125550090286902</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4289939011955163</v>
+        <v>0.4019306447646512</v>
       </c>
     </row>
     <row r="3">
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="C3" t="n">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="D3" t="n">
-        <v>0.73054849192706</v>
+        <v>0.5156937612858628</v>
       </c>
       <c r="E3" t="n">
-        <v>0.584438793541648</v>
+        <v>0.4125550090286902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5547247539179991</v>
+        <v>0.3915798855073258</v>
       </c>
     </row>
     <row r="4">
@@ -881,19 +881,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="C4" t="n">
-        <v>28000</v>
+        <v>29250</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6685677795965392</v>
+        <v>0.4629925476480081</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5348542236772315</v>
+        <v>0.3703940381184065</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4945875679293999</v>
+        <v>0.3425088152600683</v>
       </c>
     </row>
     <row r="5">
@@ -903,19 +903,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="C5" t="n">
-        <v>19000</v>
+        <v>29250</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4451202683822472</v>
+        <v>0.4629925476480081</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3560962147057978</v>
+        <v>0.3703940381184065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3208074006358538</v>
+        <v>0.3336883226291951</v>
       </c>
     </row>
     <row r="6">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C6" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.401804202378531</v>
+        <v>0.3318117786530139</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3214433619028248</v>
+        <v>0.2654494229224111</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2821309544803176</v>
+        <v>0.2329850540761508</v>
       </c>
     </row>
     <row r="7">
@@ -947,19 +947,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5321045635279211</v>
+        <v>0.3318117786530139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4256836508223369</v>
+        <v>0.2654494229224111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3640009376929152</v>
+        <v>0.2269850830943182</v>
       </c>
     </row>
     <row r="8">
@@ -969,19 +969,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5942613574275627</v>
+        <v>0.3318117786530139</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4754090859420502</v>
+        <v>0.2654494229224111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.396052049255255</v>
+        <v>0.2211396269672069</v>
       </c>
     </row>
     <row r="9">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="C9" t="n">
-        <v>18000</v>
+        <v>25000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3833156376208472</v>
+        <v>0.3318117786530139</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3066525100966778</v>
+        <v>0.2654494229224111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2488860564050627</v>
+        <v>0.2154447065355175</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.09018362151232</v>
+        <v>2.366262138834434</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.882750601024807</v>
+        <v>4.678446678005328</v>
       </c>
       <c r="F11" t="n">
-        <v>3.860893658191166</v>
+        <v>3.699346246663752</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.951077279703486</v>
+        <v>6.065608385498185</v>
       </c>
     </row>
     <row r="13">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24750</v>
+        <v>29275</v>
       </c>
     </row>
   </sheetData>
@@ -1064,11 +1064,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.362661491864415</v>
+        <v>4.176713024081303</v>
       </c>
       <c r="C2" t="n">
-        <v>4.943314719976149</v>
+        <v>4.757366252193036</v>
       </c>
       <c r="D2" t="n">
-        <v>5.52396794808788</v>
+        <v>5.338019480304768</v>
       </c>
       <c r="E2" t="n">
-        <v>6.104621176199614</v>
+        <v>5.918672708416501</v>
       </c>
       <c r="F2" t="n">
-        <v>6.685274404311345</v>
+        <v>6.499325936528232</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.590935072895884</v>
+        <v>4.365140504873533</v>
       </c>
       <c r="C3" t="n">
-        <v>5.171588301007617</v>
+        <v>4.945793732985265</v>
       </c>
       <c r="D3" t="n">
-        <v>5.752241529119349</v>
+        <v>5.526446961096998</v>
       </c>
       <c r="E3" t="n">
-        <v>6.332894757231083</v>
+        <v>6.107100189208731</v>
       </c>
       <c r="F3" t="n">
-        <v>6.913547985342813</v>
+        <v>6.687753417320462</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.819208653927353</v>
+        <v>4.553567985665763</v>
       </c>
       <c r="C4" t="n">
-        <v>5.399861882039087</v>
+        <v>5.134221213777496</v>
       </c>
       <c r="D4" t="n">
-        <v>5.980515110150819</v>
+        <v>5.714874441889228</v>
       </c>
       <c r="E4" t="n">
-        <v>6.561168338262552</v>
+        <v>6.295527670000962</v>
       </c>
       <c r="F4" t="n">
-        <v>7.141821566374283</v>
+        <v>6.876180898112692</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.047482234958822</v>
+        <v>4.741995466457993</v>
       </c>
       <c r="C5" t="n">
-        <v>5.628135463070555</v>
+        <v>5.322648694569727</v>
       </c>
       <c r="D5" t="n">
-        <v>6.208788691182287</v>
+        <v>5.903301922681459</v>
       </c>
       <c r="E5" t="n">
-        <v>6.789441919294021</v>
+        <v>6.483955150793192</v>
       </c>
       <c r="F5" t="n">
-        <v>7.370095147405751</v>
+        <v>7.064608378904923</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.275755815990291</v>
+        <v>4.930422947250223</v>
       </c>
       <c r="C6" t="n">
-        <v>5.856409044102024</v>
+        <v>5.511076175361957</v>
       </c>
       <c r="D6" t="n">
-        <v>6.437062272213756</v>
+        <v>6.091729403473689</v>
       </c>
       <c r="E6" t="n">
-        <v>7.017715500325489</v>
+        <v>6.672382631585422</v>
       </c>
       <c r="F6" t="n">
-        <v>7.598368728437221</v>
+        <v>7.253035859697153</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.98</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>6.01</v>
+        <v>5.74</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96485.20361670371</v>
+        <v>95852.78512943507</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.42903164965372</v>
+        <v>2.41311040511239</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95852.78512943507</v>
+        <v>95852.78512943508</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95852.78512943508</v>
+        <v>95852.78512943507</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.49</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95852.78512943507</v>
+        <v>103758.0162202929</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.41311040511239</v>
+        <v>2.612125961879023</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.74</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>103758.0162202929</v>
+        <v>117987.4321838371</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.612125961879023</v>
+        <v>2.970353964058965</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.19</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>117987.4321838371</v>
+        <v>126841.2910055979</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.970353964058965</v>
+        <v>3.193251387637596</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.714874441889228</v>
+        <v>4.830494066940222</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.564559894628247</v>
+        <v>4.63590237247724</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.065608385498185</v>
+        <v>5.284541354020513</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.792448433177855</v>
+        <v>1.799917969481227</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126841.2910055979</v>
+        <v>159435.6784429081</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.193251387637596</v>
+        <v>4.14040165347304</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>571.1176458623593</v>
+        <v>467.6552193412342</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>848.7733333333332</v>
+        <v>762.05</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1588.457727298479</v>
+        <v>1782.45876236643</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>319.7333333333333</v>
+        <v>262.5166666666667</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>146.457</v>
+        <v>270.983</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>362.884</v>
+        <v>189.204</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-953.932</v>
+        <v>-808.299</v>
       </c>
     </row>
     <row r="9">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-71.59699999999999</v>
+        <v>-77.06399999999999</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0</v>
+        <v>-503.6</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="B12" t="n">
-        <v>2811.894039827504</v>
+        <v>2345.904648374331</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>505321911</v>
+        <v>506029778</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.564559894628247</v>
+        <v>4.63590237247724</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.564559894628247</v>
+        <v>4.63590237247724</v>
       </c>
     </row>
     <row r="16">
@@ -793,7 +793,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -843,13 +843,13 @@
         <v>29300</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5156937612858628</v>
+        <v>0.4609591944310439</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4125550090286902</v>
+        <v>0.3687673555448352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4019306447646512</v>
+        <v>0.3592706372206074</v>
       </c>
     </row>
     <row r="3">
@@ -865,13 +865,13 @@
         <v>29300</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5156937612858628</v>
+        <v>0.4609591944310439</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4125550090286902</v>
+        <v>0.3687673555448352</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3915798855073258</v>
+        <v>0.350018484087885</v>
       </c>
     </row>
     <row r="4">
@@ -887,13 +887,13 @@
         <v>29250</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4629925476480081</v>
+        <v>0.4172465500637</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3703940381184065</v>
+        <v>0.33379724005096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3425088152600683</v>
+        <v>0.3086672177762935</v>
       </c>
     </row>
     <row r="5">
@@ -909,13 +909,13 @@
         <v>29250</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4629925476480081</v>
+        <v>0.4172465500637</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3703940381184065</v>
+        <v>0.33379724005096</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3336883226291951</v>
+        <v>0.3007182342801441</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>25000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3318117786530139</v>
+        <v>0.2997798080298943</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2654494229224111</v>
+        <v>0.2398238464239154</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2329850540761508</v>
+        <v>0.210493476356731</v>
       </c>
     </row>
     <row r="7">
@@ -953,13 +953,13 @@
         <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3318117786530139</v>
+        <v>0.2997798080298943</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2654494229224111</v>
+        <v>0.2398238464239154</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2269850830943182</v>
+        <v>0.2050727219868276</v>
       </c>
     </row>
     <row r="8">
@@ -975,13 +975,13 @@
         <v>25000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3318117786530139</v>
+        <v>0.2997798080298943</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2654494229224111</v>
+        <v>0.2398238464239154</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2211396269672069</v>
+        <v>0.1997915661377308</v>
       </c>
     </row>
     <row r="9">
@@ -997,13 +997,13 @@
         <v>25000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3318117786530139</v>
+        <v>0.2997798080298943</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2654494229224111</v>
+        <v>0.2398238464239154</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2154447065355175</v>
+        <v>0.1946464137845267</v>
       </c>
     </row>
     <row r="10">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.366262138834434</v>
+        <v>2.128678751630746</v>
       </c>
     </row>
     <row r="11">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.678446678005328</v>
+        <v>3.991120031466917</v>
       </c>
       <c r="F11" t="n">
-        <v>3.699346246663752</v>
+        <v>3.155862602389767</v>
       </c>
     </row>
     <row r="12">
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.065608385498185</v>
+        <v>5.284541354020513</v>
       </c>
     </row>
     <row r="13">
@@ -1067,8 +1067,8 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1110,19 +1110,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.176713024081303</v>
+        <v>3.328444281409754</v>
       </c>
       <c r="C2" t="n">
-        <v>4.757366252193036</v>
+        <v>3.905629662482204</v>
       </c>
       <c r="D2" t="n">
-        <v>5.338019480304768</v>
+        <v>4.482815043554653</v>
       </c>
       <c r="E2" t="n">
-        <v>5.918672708416501</v>
+        <v>5.060000424627104</v>
       </c>
       <c r="F2" t="n">
-        <v>6.499325936528232</v>
+        <v>5.63718580569955</v>
       </c>
     </row>
     <row r="3">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.365140504873533</v>
+        <v>3.502283793102539</v>
       </c>
       <c r="C3" t="n">
-        <v>4.945793732985265</v>
+        <v>4.079469174174988</v>
       </c>
       <c r="D3" t="n">
-        <v>5.526446961096998</v>
+        <v>4.656654555247437</v>
       </c>
       <c r="E3" t="n">
-        <v>6.107100189208731</v>
+        <v>5.233839936319888</v>
       </c>
       <c r="F3" t="n">
-        <v>6.687753417320462</v>
+        <v>5.811025317392335</v>
       </c>
     </row>
     <row r="4">
@@ -1154,19 +1154,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.553567985665763</v>
+        <v>3.676123304795323</v>
       </c>
       <c r="C4" t="n">
-        <v>5.134221213777496</v>
+        <v>4.253308685867773</v>
       </c>
       <c r="D4" t="n">
-        <v>5.714874441889228</v>
+        <v>4.830494066940222</v>
       </c>
       <c r="E4" t="n">
-        <v>6.295527670000962</v>
+        <v>5.407679448012672</v>
       </c>
       <c r="F4" t="n">
-        <v>6.876180898112692</v>
+        <v>5.98486482908512</v>
       </c>
     </row>
     <row r="5">
@@ -1176,19 +1176,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.741995466457993</v>
+        <v>3.849962816488108</v>
       </c>
       <c r="C5" t="n">
-        <v>5.322648694569727</v>
+        <v>4.427148197560557</v>
       </c>
       <c r="D5" t="n">
-        <v>5.903301922681459</v>
+        <v>5.004333578633006</v>
       </c>
       <c r="E5" t="n">
-        <v>6.483955150793192</v>
+        <v>5.581518959705457</v>
       </c>
       <c r="F5" t="n">
-        <v>7.064608378904923</v>
+        <v>6.158704340777904</v>
       </c>
     </row>
     <row r="6">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.930422947250223</v>
+        <v>4.023802328180892</v>
       </c>
       <c r="C6" t="n">
-        <v>5.511076175361957</v>
+        <v>4.600987709253342</v>
       </c>
       <c r="D6" t="n">
-        <v>6.091729403473689</v>
+        <v>5.178173090325791</v>
       </c>
       <c r="E6" t="n">
-        <v>6.672382631585422</v>
+        <v>5.755358471398242</v>
       </c>
       <c r="F6" t="n">
-        <v>7.253035859697153</v>
+        <v>6.332543852470689</v>
       </c>
     </row>
   </sheetData>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>5.71</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="3">
@@ -1256,7 +1256,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>5.73</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="4">
@@ -1264,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>5.74</v>
+        <v>4.85</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/hafn_fv_report.xlsx
+++ b/outputs/hafn_fv_report.xlsx
@@ -426,7 +426,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
